--- a/unanswered_questions_log.xlsx
+++ b/unanswered_questions_log.xlsx
@@ -2,41 +2,202 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="8400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Question Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -45,8 +206,206 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
-        <bgColor rgb="002F5496"/>
+        <fgColor rgb="FF2F5496"/>
+        <bgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,12 +421,125 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -77,10 +549,154 @@
       <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -91,9 +707,63 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -446,7 +1116,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -456,8 +1125,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D91"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -707,6 +1376,1789 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:01:53</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>my vision are blur what could be the reason</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:04:18</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>From today morning, my visions are blur and my eyes were paining. What could be the reason?</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:11:15</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>From today morning, my visions are blurred. What could be the reason and what I need to do?</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:11:31</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>From today morning, my visions are blurred. What could be the reason and what I need to do?</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:13:26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>suggest any hospital</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:15:48</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>what is acne</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:16:15</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>suggest any hospital</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:16:32</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>what is enzyme</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:20:02</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>my vission are blur how i need to take care of it</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:28:50</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>what is acne</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:43:20</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>How can I reduce dark spots on my face?</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:56:34</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>who is dhoni</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:46:47</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>who is dhoni</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:47:08</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>who is dhoni</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:47:29</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>iam feeling tired and fever</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:53:18</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>from today morning my vision are blur what could be the reason</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:53:40</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Today morning my visions were blurred and my eyes were paining, what could be the reason?</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:57:09</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>what is roundworms</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:38:20</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>who is dhoni</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:39:41</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>who is dhoni</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:01:07</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>what is this</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:06:17</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>my vission are blur</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:06:50</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>my vision are blur what could be gthe reason</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:07:03</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>my chest is paining</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:08:48</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Please analyze this medical image and provide guidance.
+Image Findings: I can't analyze images directly. However, if you suspect a fracture or injury in your arm, common causes can be falls or direct impact. 
+For immediate care, rest the affected arm and apply ice wrapped in a cloth to reduce swelling. Elevating the arm can also help. Avoid using the arm until you can consult a healthcare professional for an accurate evaluation and treatment. It's important to seek further medical advice to ensure proper healing.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:28:29</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>after exposing to sunlight is it possible to get skin cancer</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:28:02</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>What could it be?</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:47:51</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>what is the jersey number of MS</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:48:17</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>what is the skin tone of MS DHONI?</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:02:23</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Why do I have a headache?</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:02:53</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Why do I have a headache?</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:03:08</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>What is diabetes?</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:04:42</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>What is dermatomyositis?</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:07:43</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>How does PRP therapy work?</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:10:52</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Can skin diseases spread through WiFi?</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:11:44</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Can mobile radiation cause acne?</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:12:21</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>What is pityriasis lichenoides?</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:12:42</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>How to remove tan instantly?</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:13:58</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>What is pityriasis lichenoides?</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:40:53</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>how you will help me</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:49:01</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>how many days i need to follow this</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:42</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>how many days i need to follow this</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:51:08</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>if grade 2 means how many days i need to follow</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:52:26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>can you explain grade 4 detaily</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:53:47</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>can you explain grade 4</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:02:02</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>after exposing to sunlight is it possible to get skin cancer</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:53:45</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>what is acne</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:57:02</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>why pregnant women get dark skin</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:39</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>how many days to recover with continuous medication</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 11:39:39</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>can you explain it in simple</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 11:40:17</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>what kind of treatment i need to take</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 11:53:54</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>how many days it will take to cure this</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 11:57:43</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>can you explain this in simple</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:01:04</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>what is the enzyme and what it cause</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:01:15</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>what is the enzyme</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:02:34</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>explain it</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="45" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:12:18</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>after exposing to sunlight is it possible to get skin cancer</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="45" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:15:29</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>iam feeling headche</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:15:44</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>who is dhoni</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:16:01</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>iam feeling fever and vominting</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:54:29</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Please analyze this medical image and provide guidance.
+Image Findings: I cannot analyze images directly. However, if you're experiencing pain or discomfort in your arm, it could be due to a sprain, strain, or even a fracture.
+For mild discomfort, you can try resting the arm, applying a cold pack to reduce swelling, and gently elevating it. Over-the-counter pain relief can also help. If you notice significant swelling, persistent pain, or an inability to move your arm, it’s important to consult a healthcare professional for a proper assessment and treatment.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 16:31:35</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>What kind of picture I need to take?</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 19:49:00</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Is it dangerous?</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="45" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:20:40</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>How does it spread?</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05 11:57:28</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>can you tell about Inflammation</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 12:57:19</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>can you explain this in simple</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="45" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 12:58:31</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>explain this</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="45" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05 13:31:24</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>It is spreading slowly</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="45" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05 13:35:38</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>I have red circular patches</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="45" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05 13:36:00</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>I have red circular patches</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="45" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 19:37:12</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>After exfoliation, is it possible to get skin cancer?</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="45" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-15 07:04:50</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Please analyze this medical image and provide guidance.
+Image Findings: I can't analyze medical images. However, if you suspect an injury in the arm, possible causes might include fractures, strains, or sprains. 
+For minor injuries, rest the affected area, apply ice to reduce swelling, and elevate it when possible. Over-the-counter pain relievers may help with discomfort. If there is significant pain, swelling, or inability to move the arm, seeking professional medical attention is important. Your well-being is key, so don’t hesitate to get help if needed.</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22 15:18:45</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>What is blue skin syndrome?</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="45" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22 15:18:59</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>What is blue skin syndrome?</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="45" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 15:22:31</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>I think my hand fractured, so what I need to do?
+Image Findings: If you suspect a fracture in your hand, it's important to keep it still and avoid using it. Try gently applying ice wrapped in a cloth to reduce swelling. Elevating your hand can also help. Over-the-counter pain relief can be used if needed. 
+However, it's crucial to seek professional medical evaluation to confirm the injury and discuss further treatment options. Take care and try to get help soon.</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="45" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:52:02</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>What is this?
+Image Findings: This appears to be an X-ray showing a fracture in the arm. Fractures can occur from falls or impacts. 
+For immediate care at home, you can:
+- Rest the affected arm and avoid using it.
+- Apply a cold pack wrapped in a cloth to reduce swelling.
+- Keep the arm elevated if possible.
+- If pain is present, over-the-counter pain relief can be helpful.
+It's important to see a healthcare professional for proper assessment and treatment. They may recommend further imaging and the appropriate immobilization or treatment plan. Remember to take care of yourself and seek medical advice.</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="45" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02 07:54:37</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Please analyze this medical image and provide guidance.
+Image Findings: I can't analyze images directly, but the appearance you described suggests a possible skin condition in cattle, such as bovine warts or other viral infections. 
+It's important to keep the animal in a clean and dry environment. Regularly grooming them can help reduce irritation. If possible, consider consulting a veterinarian for specific treatments or vaccinations. Monitoring for any signs of distress or worsening condition is also essential. Always ensure your animal is comfortable and hydrated.</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="45" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02 08:22:34</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Please analyze this medical image and provide guidance.
+Image Findings: I'm unable to analyze the image directly, but if you are seeing unusual lumps or nodules on an animal, it could be due to several potential causes, such as skin infections, parasites, or a condition known as lump jaw. It's important to observe any other symptoms the animal may have, such as loss of appetite or lethargy.
+For simple home remedies, ensuring the animal is in a clean environment can help prevent further issues. You can also consult with a veterinarian for a proper diagnosis and treatment plan. Regular check-ups will help keep your animal healthy as well.</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>UNRELATED</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>I'm a dermatology assistant and can only help with skin, hair, nail, or skincare-related questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="45" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02 08:22:51</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Please analyze this medical image and provide guidance.
+Image Findings: I can't analyze images, but if you're noticing symptoms like bumps or lesions on a cow, it may be a skin condition or an infection. Common causes include insect bites or viral infections.
+For home care, ensure the animal stays in a clean environment and consider using a mild antiseptic to prevent infection. If there is significant discomfort or if the condition worsens, it's best to consult a veterinarian who can provide specific guidance and treatment options. Keeping the animal well-hydrated and nourished can also support its recovery.</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="45" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02 08:23:21</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Please analyze this medical image and provide guidance.
+Image Findings: I cannot analyze medical images as I cannot see or recognize them. However, if an animal appears to have unusual growths or skin conditions, these may be due to infections, parasites, or environmental factors.
+For general care, ensure the animal has a clean living environment, good nutrition, and access to fresh water. Observe for any changes in behavior or eating habits. If symptoms persist or worsen, it's best to consult a veterinarian for proper diagnosis and treatment.</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>NOT_IN_CONTEXT</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>I acknowledge your question, but this topic is currently not covered in the uploaded knowledge base. Please consult a dermatologist or refer to a broader medical resource for more information.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
